--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>131204756</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>131204756</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>131204756</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>131204756</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>131204756</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73538876</v>
+        <v>131204756</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ällmora 450m SV, Srm</t>
+          <t>Ällmora SV om , Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605026.1286832583</v>
+        <v>604965</v>
       </c>
       <c r="R2" t="n">
-        <v>6546030.530157625</v>
+        <v>6546211</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,14 +766,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>betad skog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93222217</v>
+        <v>133995720</v>
       </c>
       <c r="B3" t="n">
-        <v>81962</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,40 +795,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>232272</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ällmora 350m SV om, Srm</t>
+          <t>Ällmora 400m S, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604944.0852762922</v>
+        <v>605084</v>
       </c>
       <c r="R3" t="n">
-        <v>6546126.100557497</v>
+        <v>6546080</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,9 +871,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,60 +891,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131204756</v>
+        <v>73538876</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ällmora SV om , Srm</t>
+          <t>Ällmora 450m SV, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604965</v>
+        <v>605026</v>
       </c>
       <c r="R4" t="n">
-        <v>6546211</v>
+        <v>6546031</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,8 +974,14 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>betad skog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1024,6 +995,433 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103549765</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ällmora 400 m s-ut, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>605092</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6546086</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103550552</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ällmora 400m S, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>605084</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6546080</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103550535</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ällmora 400m S, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>605084</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546080</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>93222217</v>
+      </c>
+      <c r="B8" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ällmora 350m SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>604944</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546126</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,32 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73538876</v>
+        <v>135480131</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>110198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>220320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,14 +926,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ällmora 450m SV, Srm</t>
+          <t>Ällmora SSV om , Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605026</v>
+        <v>605019</v>
       </c>
       <c r="R4" t="n">
-        <v>6546031</v>
+        <v>6546203</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +980,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>betad skog</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103549765</v>
+        <v>73538876</v>
       </c>
       <c r="B5" t="n">
-        <v>106156</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,14 +1033,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ällmora 400 m s-ut, Srm</t>
+          <t>Ällmora 450m SV, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605092</v>
+        <v>605026</v>
       </c>
       <c r="R5" t="n">
-        <v>6546086</v>
+        <v>6546031</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hagmark</t>
+          <t>betad skog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103550552</v>
+        <v>103549765</v>
       </c>
       <c r="B6" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,14 +1140,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ällmora 400m S, Srm</t>
+          <t>ällmora 400 m s-ut, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605084</v>
+        <v>605092</v>
       </c>
       <c r="R6" t="n">
-        <v>6546080</v>
+        <v>6546086</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103550535</v>
+        <v>103550552</v>
       </c>
       <c r="B7" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,21 +1223,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>93222217</v>
+        <v>103550535</v>
       </c>
       <c r="B8" t="n">
-        <v>84148</v>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,40 +1330,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232272</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ällmora 350m SV om, Srm</t>
+          <t>Ällmora 400m S, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604944</v>
+        <v>605084</v>
       </c>
       <c r="R8" t="n">
-        <v>6546126</v>
+        <v>6546080</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,12 +1388,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,9 +1406,9 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1422,6 +1423,112 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>93222217</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ällmora 350m SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>604944</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6546126</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131204756</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133995720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135480131</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73538876</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549765</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103550552</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103550535</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,8 +1569,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93222217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>135480131</v>
       </c>
       <c r="B4" t="n">
-        <v>110198</v>
+        <v>110254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>135480131</v>
       </c>
       <c r="B4" t="n">
-        <v>110254</v>
+        <v>110281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,32 +906,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73538876</v>
+        <v>135480131</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>110286</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>220320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ällmora 450m SV, Srm</t>
+          <t>Ällmora SSV om , Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605026</v>
+        <v>605019</v>
       </c>
       <c r="R4" t="n">
-        <v>6546031</v>
+        <v>6546203</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>betad skog</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1012,38 +1012,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73538876</t>
+          <t>https://artportalen.se/Sighting/135480131</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103549765</v>
+        <v>73538876</v>
       </c>
       <c r="B5" t="n">
-        <v>106156</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,14 +1053,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ällmora 400 m s-ut, Srm</t>
+          <t>Ällmora 450m SV, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605092</v>
+        <v>605026</v>
       </c>
       <c r="R5" t="n">
-        <v>6546086</v>
+        <v>6546031</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hagmark</t>
+          <t>betad skog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,16 +1124,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103549765</t>
+          <t>https://artportalen.se/Sighting/73538876</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103550552</v>
+        <v>103549765</v>
       </c>
       <c r="B6" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,14 +1165,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ällmora 400m S, Srm</t>
+          <t>ällmora 400 m s-ut, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605084</v>
+        <v>605092</v>
       </c>
       <c r="R6" t="n">
-        <v>6546080</v>
+        <v>6546086</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1236,16 +1236,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103550552</t>
+          <t>https://artportalen.se/Sighting/103549765</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103550535</v>
+        <v>103550552</v>
       </c>
       <c r="B7" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1348,16 +1348,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103550535</t>
+          <t>https://artportalen.se/Sighting/103550552</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>93222217</v>
+        <v>103550535</v>
       </c>
       <c r="B8" t="n">
-        <v>84148</v>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,40 +1365,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232272</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ällmora 350m SV om, Srm</t>
+          <t>Ällmora 400m S, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604944</v>
+        <v>605084</v>
       </c>
       <c r="R8" t="n">
-        <v>6546126</v>
+        <v>6546080</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,12 +1423,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,9 +1441,9 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1458,6 +1459,117 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103550535</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>93222217</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ällmora 350m SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>604944</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6546126</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/93222217</t>
         </is>
@@ -1472,6 +1584,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>135480131</v>
       </c>
       <c r="B4" t="n">
-        <v>110286</v>
+        <v>110288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>135480131</v>
       </c>
       <c r="B4" t="n">
-        <v>110288</v>
+        <v>110311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4155-2024 artfynd.xlsx
+++ b/artfynd/A 4155-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>135480131</v>
       </c>
       <c r="B4" t="n">
-        <v>110311</v>
+        <v>110313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
